--- a/data/trans_orig/IP18A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Estudios-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>5188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>68345</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>138595</t>
+          <t>139555</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365446</t>
+          <t>365221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371466</t>
+          <t>371596</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>404490</t>
+          <t>405150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>772234</t>
+          <t>773307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>780073</t>
+          <t>780070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150278</t>
+          <t>150277</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136991</t>
+          <t>137045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289459</t>
+          <t>289736</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589231</t>
+          <t>588920</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>595987</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>615298</t>
+          <t>615059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>622106</t>
+          <t>621913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207741</t>
+          <t>1207681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1217017</t>
+          <t>1216881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82429</t>
+          <t>82417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73240</t>
+          <t>73214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158773</t>
+          <t>158050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413208</t>
+          <t>413438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>420305</t>
+          <t>420312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>458986</t>
+          <t>459650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>465665</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>875076</t>
+          <t>875343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>884559</t>
+          <t>884565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152046</t>
+          <t>151353</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>154196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160937</t>
+          <t>160938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>308782</t>
+          <t>309165</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316329</t>
+          <t>316734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20211</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>653426</t>
+          <t>653253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>661605</t>
+          <t>661085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>692598</t>
+          <t>692709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702568</t>
+          <t>702248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1349900</t>
+          <t>1349800</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1361524</t>
+          <t>1361608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112630</t>
+          <t>112740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10094</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422931</t>
+          <t>422616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>431001</t>
+          <t>430637</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422198</t>
+          <t>421066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431900</t>
+          <t>431883</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>847454</t>
+          <t>848499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>860656</t>
+          <t>861640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148812</t>
+          <t>148556</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>166518</t>
+          <t>166983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317756</t>
+          <t>317285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323617</t>
+          <t>323618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>627562</t>
+          <t>627299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>636592</t>
+          <t>636653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>653510</t>
+          <t>653672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664151</t>
+          <t>664668</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1284552</t>
+          <t>1284980</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1298611</t>
+          <t>1299068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5695</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10284</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61778</t>
+          <t>62129</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81767</t>
+          <t>81918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90048</t>
+          <t>89970</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>145905</t>
+          <t>146574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155022</t>
+          <t>155663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27116</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54184</t>
+          <t>53937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58032</t>
+          <t>58021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12147</t>
+          <t>12110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94027</t>
+          <t>93669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99517</t>
+          <t>99164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119445</t>
+          <t>119482</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129359</t>
+          <t>129204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216887</t>
+          <t>217059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227523</t>
+          <t>227611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP18A05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP18A05-Estudios-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2007 (tasa de respuesta: 99,73%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2007 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,107 +723,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1662</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6086</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1662</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5711</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5995</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1662</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5188</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72394</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67970</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70687</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72394</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>68345</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139555</t>
+          <t>138748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>74056</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70687</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70687</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70687</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>74056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2911</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7105</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6551</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1380</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4161</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1567</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1179,74 +1179,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>407931</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>405183</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>557</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>369415</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>365221</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>371596</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>365775</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>371591</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,8%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>407931</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>405150</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1173</t>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>773307</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>780070</t>
+          <t>779892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>409311</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>561</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>372326</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>409311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,102 +1414,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2433</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4017</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2876</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3840</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1276</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4479</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>139438</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>137488</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>153501</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>150277</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>149094</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,49%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,63%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>139438</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>137045</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>432</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>289736</t>
+          <t>290375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154294</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1757,67 +1757,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8492</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8387</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8668</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8229</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13617</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>619763</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>614796</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>622113</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>886</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>593603</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>588920</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>595978</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>588639</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>595872</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>933</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>619763</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>615059</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>621913</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1207681</t>
+          <t>1206978</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1216881</t>
+          <t>1217120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>623288</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>597307</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>597307</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>597307</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>623288</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2141,13 +2141,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2012 (tasa de respuesta: 98,05%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2012 (tasa de respuesta: 98,05%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2331,102 +2331,102 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3607</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3792</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3772</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -2439,74 +2439,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76246</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>72562</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>85368</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82417</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>82232</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>86024</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,24%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76246</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>73214</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>230</t>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158050</t>
+          <t>158170</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76986</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>86024</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>86024</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>86024</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2923</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7220</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4166</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1394</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8268</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8457</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2923</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6755</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>463482</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>459185</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>465662</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>417540</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>413438</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>420312</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>413249</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>419860</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>661</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>463482</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>459650</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>465665</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>875343</t>
+          <t>875291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>884565</t>
+          <t>884585</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466405</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466405</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466405</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>611</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>421706</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>421706</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>421706</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>466405</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>466405</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>466405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,74 +3012,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4214</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1566</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8764</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4713</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4709</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4214</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8728</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>10189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158710</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154160</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161358</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155276</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>151353</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>151357</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>156066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,49%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158710</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154196</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>160938</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>443</t>
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309165</t>
+          <t>308801</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>316734</t>
+          <t>316820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>162924</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>162924</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>162924</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>162924</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>162924</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>162924</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4256</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13773</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5612</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10542</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10814</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4067</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13606</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>698438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>692542</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>702059</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,88%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>947</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>658183</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>653253</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>661085</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>652981</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>661164</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,15%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>698438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>692709</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>702248</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1349800</t>
+          <t>1349826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1361608</t>
+          <t>1361878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>706315</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>706315</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>706315</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>955</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>663795</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>663795</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>663795</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>706315</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>706315</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>706315</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3744,13 +3744,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2016 (tasa de respuesta: 98,16%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2016 (tasa de respuesta: 98,16%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,107 +3929,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1221</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4385</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4240</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53439</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50275</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50522</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>54660</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>168</t>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112740</t>
+          <t>112485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62065</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>54660</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62065</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14993</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5012</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2388</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10409</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2189</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10638</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8052</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4055</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>14872</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20464</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>427886</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>420945</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>431834</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,15%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>428013</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>422616</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>430637</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>422387</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>430836</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>427886</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>421066</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>431883</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>848499</t>
+          <t>847293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>861640</t>
+          <t>860949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>435938</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>435938</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>435938</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>433025</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>433025</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>433025</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>435938</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>435938</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>435938</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4620,67 +4620,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4536</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1189</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4104</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1472</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4694</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -4728,74 +4728,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>170205</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>167141</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>171677</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,36%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151471</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>148556</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148837</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>152660</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>170205</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>166983</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>171677</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>472</t>
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317285</t>
+          <t>317784</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323618</t>
+          <t>323689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171677</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171677</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171677</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152660</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152660</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152660</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171677</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171677</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16503</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7422</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3692</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13046</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5013</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16009</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>24821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>660157</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>653178</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>664606</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>632923</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>627299</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>636653</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>626381</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>636206</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>660157</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>653672</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>664668</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1284980</t>
+          <t>1285204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1299068</t>
+          <t>1299136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>669681</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>640345</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>640345</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>669681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5347,13 +5347,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según su última visita al médico fue por dispensación de recetas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si su última consulta médica fue por dispensación de recetas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4749</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5552</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -5650,69 +5650,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>3871</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5954</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7513</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4685</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9434</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>79,64%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>49,66%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>22</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3601</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1189</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10711</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4109</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5253</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3795</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -5988,74 +5988,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>80206</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73096</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82618</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>64910</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62129</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>61888</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57973</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>63226</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>91,69%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>87454</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>81918</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>89970</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>89,77%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>226</t>
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>152364</t>
+          <t>142094</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146574</t>
+          <t>135534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155663</t>
+          <t>145092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>83807</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66238</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91249</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>147033</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1568</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4219</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1568</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>25963</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23312</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27137</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>24927</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>56873</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53937</t>
+          <t>50855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58021</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28824</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27531</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30909</t>
+          <t>26332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58441</t>
+          <t>55155</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2435</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12689</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6645</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>116209</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>109033</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>119287</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>97418</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>93669</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>99164</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,11%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>125876</t>
+          <t>92769</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>88494</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129204</t>
+          <t>94560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>223294</t>
+          <t>208978</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217059</t>
+          <t>202464</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227611</t>
+          <t>212727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
